--- a/final/688758_赛分科技_三表抽取.xlsx
+++ b/final/688758_赛分科技_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,6 +454,11 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -480,6 +486,11 @@
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -507,6 +518,11 @@
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -534,6 +550,11 @@
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -561,6 +582,11 @@
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -588,6 +614,11 @@
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -615,6 +646,11 @@
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -642,6 +678,11 @@
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -669,6 +710,11 @@
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -696,6 +742,11 @@
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -723,6 +774,11 @@
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -750,6 +806,11 @@
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -777,6 +838,11 @@
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -804,6 +870,11 @@
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -831,6 +902,11 @@
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -858,323 +934,9 @@
           <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以人民币 1.85亿元认购。</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>59</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>源峰磐赛</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>157.1815</v>
-      </c>
-      <c r="E17" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F17" t="n">
-        <v>127.24</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Markdown: 源峰磐赛认购1571815股/20000.0万元@127.24元/股</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>59</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>珠海峦恒</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>62.8726</v>
-      </c>
-      <c r="E18" t="n">
-        <v>8000</v>
-      </c>
-      <c r="F18" t="n">
-        <v>127.24</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Markdown: 珠海峦恒认购628726股/8000.0万元@127.24元/股</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>59</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>高瓴祈睿</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>62.8726</v>
-      </c>
-      <c r="E19" t="n">
-        <v>8000</v>
-      </c>
-      <c r="F19" t="n">
-        <v>127.24</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Markdown: 高瓴祈睿认购628726股/8000.0万元@127.24元/股</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>59</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>国药中生</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>46.1846</v>
-      </c>
-      <c r="E20" t="n">
-        <v>5876.59</v>
-      </c>
-      <c r="F20" t="n">
-        <v>127.24</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Markdown: 国药中生认购461846股/5876.59万元@127.24元/股</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>59</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>圣成投资</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0.9699</v>
-      </c>
-      <c r="E21" t="n">
-        <v>123.41</v>
-      </c>
-      <c r="F21" t="n">
-        <v>127.24</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Markdown: 圣成投资认购9699股/123.41万元@127.24元/股</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>59</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>国药二期</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>15.5625</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1980.2</v>
-      </c>
-      <c r="F22" t="n">
-        <v>127.24</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Markdown: 国药二期认购155625股/1980.2万元@127.24元/股</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>59</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>圣祁投资</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0.1556</v>
-      </c>
-      <c r="E23" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F23" t="n">
-        <v>127.24</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Markdown: 圣祁投资认购1556股/19.8万元@127.24元/股</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>59</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>夏尔巴二期</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>39.2954</v>
-      </c>
-      <c r="E24" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F24" t="n">
-        <v>127.24</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Markdown: 夏尔巴二期认购392954股/5000.0万元@127.24元/股</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>59</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>甘李药业</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>23.5772</v>
-      </c>
-      <c r="E25" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F25" t="n">
-        <v>127.24</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Markdown: 甘李药业认购235772股/3000.0万元@127.24元/股</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>59</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2021-11-10</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>吴征涛</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>15.7182</v>
-      </c>
-      <c r="E26" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F26" t="n">
-        <v>127.24</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Markdown: 吴征涛认购157182股/2000.0万元@127.24元/股</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>60</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2021-12-06</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>聚贝投资</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.7886</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F27" t="n">
-        <v>127.24</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>赛分科技增发股份117,886股,由聚贝投资以1500万元认购</t>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
@@ -1189,7 +951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J213"/>
+  <dimension ref="A1:K273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1243,10 +1005,15 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1277,10 +1044,15 @@
           <t>Markdown表格: （一）公司前身赛分有限的设立情况 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1311,10 +1083,15 @@
           <t>Markdown表格: （一）公司前身赛分有限的设立情况 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1345,10 +1122,15 @@
           <t>Markdown表格: （一）公司前身赛分有限的设立情况 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1377,10 +1159,15 @@
           <t>Markdown表格: （一）公司前身赛分有限的设立情况 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1411,10 +1198,15 @@
           <t>Markdown表格: 报告期初 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1445,10 +1237,15 @@
           <t>Markdown表格: 报告期初 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1479,10 +1276,15 @@
           <t>Markdown表格: 报告期初 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1513,10 +1315,15 @@
           <t>Markdown表格: 报告期初 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1547,10 +1354,15 @@
           <t>Markdown表格: 报告期初 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1581,10 +1393,15 @@
           <t>Markdown表格: 报告期初 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1615,10 +1432,15 @@
           <t>Markdown表格: 报告期初 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1649,10 +1471,15 @@
           <t>Markdown表格: 报告期初 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1683,10 +1510,15 @@
           <t>Markdown表格: 报告期初 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1717,10 +1549,15 @@
           <t>Markdown表格: 报告期初 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1751,10 +1588,15 @@
           <t>Markdown表格: 报告期初 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1785,10 +1627,15 @@
           <t>Markdown表格: 报告期初 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1819,10 +1666,15 @@
           <t>Markdown表格: 报告期初 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1853,10 +1705,15 @@
           <t>Markdown表格: 报告期初 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1887,10 +1744,15 @@
           <t>Markdown表格: 报告期初 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1921,10 +1783,15 @@
           <t>Markdown表格: 报告期初 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1953,10 +1820,15 @@
           <t>Markdown表格: 报告期初 | 设立时, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1987,10 +1859,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 报告期初, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2021,10 +1898,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 报告期初, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2055,10 +1937,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 报告期初, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2089,10 +1976,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 报告期初, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2123,10 +2015,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 报告期初, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2157,10 +2054,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 报告期初, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2191,10 +2093,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 报告期初, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2225,10 +2132,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 报告期初, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2259,10 +2171,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 报告期初, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2293,10 +2210,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 报告期初, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2327,10 +2249,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 报告期初, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2361,10 +2288,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 报告期初, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2395,10 +2327,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 报告期初, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2429,10 +2366,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 报告期初, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2463,10 +2405,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 报告期初, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2497,10 +2444,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 报告期初, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2531,10 +2483,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 报告期初, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2565,10 +2522,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 报告期初, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2599,10 +2561,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 报告期初, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2633,10 +2600,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 报告期初, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2667,10 +2639,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 报告期初, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2699,10 +2676,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 报告期初, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2733,10 +2715,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 2、2021年 8月，报告期内第二次股权转让, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2767,10 +2754,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 2、2021年 8月，报告期内第二次股权转让, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2801,10 +2793,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 2、2021年 8月，报告期内第二次股权转让, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2835,10 +2832,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 2、2021年 8月，报告期内第二次股权转让, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2869,10 +2871,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 2、2021年 8月，报告期内第二次股权转让, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2903,10 +2910,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 2、2021年 8月，报告期内第二次股权转让, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2937,10 +2949,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 2、2021年 8月，报告期内第二次股权转让, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2971,10 +2988,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 2、2021年 8月，报告期内第二次股权转让, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -3005,10 +3027,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 2、2021年 8月，报告期内第二次股权转让, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -3039,10 +3066,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 2、2021年 8月，报告期内第二次股权转让, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -3073,10 +3105,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 2、2021年 8月，报告期内第二次股权转让, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -3107,10 +3144,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 2、2021年 8月，报告期内第二次股权转让, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -3141,10 +3183,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 2、2021年 8月，报告期内第二次股权转让, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -3175,10 +3222,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 2、2021年 8月，报告期内第二次股权转让, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -3209,10 +3261,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 2、2021年 8月，报告期内第二次股权转让, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -3243,10 +3300,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 2、2021年 8月，报告期内第二次股权转让, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -3277,10 +3339,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 2、2021年 8月，报告期内第二次股权转让, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -3311,10 +3378,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 2、2021年 8月，报告期内第二次股权转让, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3345,10 +3417,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 2、2021年 8月，报告期内第二次股权转让, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -3379,10 +3456,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 2、2021年 8月，报告期内第二次股权转让, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -3413,10 +3495,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 2、2021年 8月，报告期内第二次股权转让, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -3445,10 +3532,15 @@
           <t>Markdown表格: （2）报告期内第一次增资 | 2、2021年 8月，报告期内第二次股权转让, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -3479,10 +3571,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -3513,10 +3610,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -3547,10 +3649,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -3581,10 +3688,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -3615,10 +3727,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -3649,10 +3766,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -3683,10 +3805,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -3717,10 +3844,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -3751,10 +3883,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -3785,10 +3922,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -3819,10 +3961,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -3853,10 +4000,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -3887,10 +4039,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3921,10 +4078,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -3955,10 +4117,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -3989,10 +4156,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -4023,10 +4195,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -4057,10 +4234,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -4091,10 +4273,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -4125,10 +4312,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -4159,10 +4351,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -4193,10 +4390,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -4227,10 +4429,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -4261,10 +4468,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -4295,10 +4507,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -4329,10 +4546,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -4363,10 +4585,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -4397,10 +4624,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -4431,10 +4663,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -4465,10 +4702,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -4499,10 +4741,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -4531,10 +4778,15 @@
           <t>Markdown表格: 4、2021年 11月，报告期内第二次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -4565,10 +4817,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -4599,10 +4856,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -4633,10 +4895,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -4667,10 +4934,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -4701,10 +4973,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -4735,10 +5012,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -4769,10 +5051,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -4803,10 +5090,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -4837,10 +5129,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -4871,10 +5168,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -4905,10 +5207,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -4939,10 +5246,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -4973,10 +5285,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -5007,10 +5324,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -5041,10 +5363,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -5075,10 +5402,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -5109,10 +5441,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -5143,10 +5480,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -5177,10 +5519,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -5211,10 +5558,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -5245,10 +5597,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -5279,10 +5636,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -5313,10 +5675,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -5347,10 +5714,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -5381,10 +5753,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -5415,10 +5792,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -5449,10 +5831,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -5483,10 +5870,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -5517,10 +5909,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -5551,10 +5948,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -5585,10 +5987,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -5619,10 +6026,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -5651,10 +6063,15 @@
           <t>Markdown表格: 5、2021年 12月，报告期内第三次增资 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -5685,10 +6102,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -5719,10 +6141,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -5753,10 +6180,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -5787,10 +6219,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -5821,10 +6258,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -5855,10 +6297,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -5889,10 +6336,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -5923,10 +6375,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -5957,10 +6414,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -5991,10 +6453,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -6025,10 +6492,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -6059,10 +6531,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -6093,10 +6570,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -6127,10 +6609,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -6161,10 +6648,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -6195,10 +6687,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -6229,10 +6726,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -6263,10 +6765,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -6297,10 +6804,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -6331,10 +6843,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -6365,10 +6882,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -6399,10 +6921,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -6433,10 +6960,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -6467,10 +6999,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -6501,10 +7038,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -6535,10 +7077,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -6569,10 +7116,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -6603,10 +7155,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -6637,10 +7194,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -6671,10 +7233,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -6705,10 +7272,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -6739,10 +7311,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -6771,10 +7348,15 @@
           <t>Markdown表格: 6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -6805,10 +7387,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -6839,10 +7426,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -6873,10 +7465,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -6907,10 +7504,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -6941,10 +7543,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -6975,10 +7582,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -7009,10 +7621,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -7043,10 +7660,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -7077,10 +7699,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -7111,10 +7738,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -7145,10 +7777,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -7179,10 +7816,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -7213,10 +7855,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -7247,10 +7894,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -7281,10 +7933,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -7315,10 +7972,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -7349,10 +8011,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -7383,10 +8050,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -7417,10 +8089,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -7451,10 +8128,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -7485,10 +8167,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -7519,10 +8206,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -7553,10 +8245,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -7587,10 +8284,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -7621,10 +8323,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -7655,10 +8362,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -7689,10 +8401,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -7723,10 +8440,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -7757,10 +8479,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -7791,10 +8518,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -7825,10 +8557,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -7859,10 +8596,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -7891,10 +8633,15 @@
           <t>Markdown表格: （一）公司股权关系 | 增资完成后, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -7915,7 +8662,7 @@
       </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="n">
-        <v>143.44885</v>
+        <v>143.4488</v>
       </c>
       <c r="I198" t="n">
         <v>17.3873</v>
@@ -7925,10 +8672,15 @@
           <t>Markdown表格: （二）实际控制人控制的其他企业情况 | 1、苏州贤达, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -7959,10 +8711,15 @@
           <t>Markdown表格: （二）实际控制人控制的其他企业情况 | 1、苏州贤达, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -7993,10 +8750,15 @@
           <t>Markdown表格: （二）实际控制人控制的其他企业情况 | 1、苏州贤达, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -8027,10 +8789,15 @@
           <t>Markdown表格: （二）实际控制人控制的其他企业情况 | 1、苏州贤达, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -8061,10 +8828,15 @@
           <t>Markdown表格: （二）实际控制人控制的其他企业情况 | 1、苏州贤达, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -8095,10 +8867,15 @@
           <t>Markdown表格: （二）实际控制人控制的其他企业情况 | 1、苏州贤达, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -8129,10 +8906,15 @@
           <t>Markdown表格: （二）实际控制人控制的其他企业情况 | 1、苏州贤达, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -8163,10 +8945,15 @@
           <t>Markdown表格: （二）实际控制人控制的其他企业情况 | 1、苏州贤达, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -8197,10 +8984,15 @@
           <t>Markdown表格: （二）实际控制人控制的其他企业情况 | 1、苏州贤达, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -8231,10 +9023,15 @@
           <t>Markdown表格: （二）实际控制人控制的其他企业情况 | 1、苏州贤达, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -8265,10 +9062,15 @@
           <t>Markdown表格: （二）实际控制人控制的其他企业情况 | 1、苏州贤达, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -8299,10 +9101,15 @@
           <t>Markdown表格: （二）实际控制人控制的其他企业情况 | 1、苏州贤达, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -8323,7 +9130,7 @@
       </c>
       <c r="G210" t="inlineStr"/>
       <c r="H210" t="n">
-        <v>33.20995</v>
+        <v>33.2099</v>
       </c>
       <c r="I210" t="n">
         <v>4.0253</v>
@@ -8333,10 +9140,15 @@
           <t>Markdown表格: （二）实际控制人控制的其他企业情况 | 1、苏州贤达, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -8367,10 +9179,15 @@
           <t>Markdown表格: （二）实际控制人控制的其他企业情况 | 1、苏州贤达, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -8401,10 +9218,15 @@
           <t>Markdown表格: （二）实际控制人控制的其他企业情况 | 1、苏州贤达, 比例合计100.0%</t>
         </is>
       </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -8431,6 +9253,3908 @@
       <c r="J213" t="inlineStr">
         <is>
           <t>Markdown表格: （二）实际控制人控制的其他企业情况 | 1、苏州贤达, 比例合计100.0%</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>markdown_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>63</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>9236.4177</v>
+      </c>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>63</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>3220</v>
+      </c>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>63</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>3102</v>
+      </c>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>63</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>2960</v>
+      </c>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>63</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>2875</v>
+      </c>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>63</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>63</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>1542</v>
+      </c>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>63</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>1322</v>
+      </c>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>63</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>1216</v>
+      </c>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>63</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>1125</v>
+      </c>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>63</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>骏耀投资</t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>1095</v>
+      </c>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>63</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="G225" t="n">
+        <v>1095</v>
+      </c>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>63</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="G226" t="n">
+        <v>798</v>
+      </c>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>63</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="G227" t="n">
+        <v>547</v>
+      </c>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>63</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="G228" t="n">
+        <v>140</v>
+      </c>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>63</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="G229" t="n">
+        <v>304</v>
+      </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>63</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="G230" t="n">
+        <v>304</v>
+      </c>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>63</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="G231" t="n">
+        <v>407</v>
+      </c>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>63</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>源峰磐赛</t>
+        </is>
+      </c>
+      <c r="G232" t="n">
+        <v>1520</v>
+      </c>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>63</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>珠海峦恒</t>
+        </is>
+      </c>
+      <c r="G233" t="n">
+        <v>1216</v>
+      </c>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>63</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>高瓴祈睿</t>
+        </is>
+      </c>
+      <c r="G234" t="n">
+        <v>912</v>
+      </c>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>63</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>国药中生</t>
+        </is>
+      </c>
+      <c r="G235" t="n">
+        <v>760</v>
+      </c>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>63</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>圣成投资</t>
+        </is>
+      </c>
+      <c r="G236" t="n">
+        <v>608</v>
+      </c>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>63</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>国药二期</t>
+        </is>
+      </c>
+      <c r="G237" t="n">
+        <v>456</v>
+      </c>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>63</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>圣祁投资</t>
+        </is>
+      </c>
+      <c r="G238" t="n">
+        <v>304</v>
+      </c>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>63</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>夏尔巴二期</t>
+        </is>
+      </c>
+      <c r="G239" t="n">
+        <v>304</v>
+      </c>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>63</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>甘李药业</t>
+        </is>
+      </c>
+      <c r="G240" t="n">
+        <v>304</v>
+      </c>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>63</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>吴征涛</t>
+        </is>
+      </c>
+      <c r="G241" t="n">
+        <v>370.8394</v>
+      </c>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>63</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>t6</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>2021年12月资本公积转增股本后股权结构</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>36648.8394</v>
+      </c>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>聚贝投资</t>
+        </is>
+      </c>
+      <c r="G242" t="n">
+        <v>179</v>
+      </c>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>本次转增完成后，公司股本总数由 31,868,556 股变更为 366,488,394 股</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>59</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="G243" t="n">
+        <v>803.1668</v>
+      </c>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="n">
+        <v>25.2961</v>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东黄学英持有8031668股，持股比例25.2961%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>59</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="G244" t="n">
+        <v>280</v>
+      </c>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="n">
+        <v>8.8187</v>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东周金清持有2800000股，持股比例8.8187%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>59</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="G245" t="n">
+        <v>270</v>
+      </c>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="n">
+        <v>8.5038</v>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东高新同华持有2700000股，持股比例8.5038%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>59</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="G246" t="n">
+        <v>257.4</v>
+      </c>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="n">
+        <v>8.1069</v>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东陆民持有2574000股，持股比例8.1069%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>59</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="G247" t="n">
+        <v>250.0615</v>
+      </c>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="n">
+        <v>7.8758</v>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东国寿疌泉持有2500615股，持股比例7.8758%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>59</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="G248" t="n">
+        <v>175.1887</v>
+      </c>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="n">
+        <v>5.5176</v>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东华泰大健康一号持有1751887股，持股比例5.5176%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>59</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>源峰磐赛</t>
+        </is>
+      </c>
+      <c r="G249" t="n">
+        <v>157.1815</v>
+      </c>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="n">
+        <v>4.9505</v>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东源峰磐赛持有1571815股，持股比例4.9505%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>59</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="G250" t="n">
+        <v>134.15</v>
+      </c>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="n">
+        <v>4.2251</v>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东苏州贤达持有1341500股，持股比例4.2251%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>59</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="G251" t="n">
+        <v>126.3621</v>
+      </c>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="n">
+        <v>3.9798</v>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东复星惟盈持有1263621股，持股比例3.9798%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>59</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>苏州博达</t>
+        </is>
+      </c>
+      <c r="G252" t="n">
+        <v>114.9389</v>
+      </c>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东苏州博达持有1149389股，持股比例3.62%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>59</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>苏州杰贤</t>
+        </is>
+      </c>
+      <c r="G253" t="n">
+        <v>69.48</v>
+      </c>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="n">
+        <v>2.1883</v>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东苏州杰贤持有694800股，持股比例2.1883%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>59</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>潘鼎</t>
+        </is>
+      </c>
+      <c r="G254" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="n">
+        <v>1.9905</v>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东潘鼎持有632000股，持股比例1.9905%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>59</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>珠海峦恒</t>
+        </is>
+      </c>
+      <c r="G255" t="n">
+        <v>62.8726</v>
+      </c>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="n">
+        <v>1.9802</v>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东珠海峦恒持有628726股，持股比例1.9802%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>59</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>高瓴祈睿</t>
+        </is>
+      </c>
+      <c r="G256" t="n">
+        <v>62.8726</v>
+      </c>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="n">
+        <v>1.9802</v>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东高瓴祈睿持有628726股，持股比例1.9802%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>59</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>海佳同康</t>
+        </is>
+      </c>
+      <c r="G257" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="n">
+        <v>1.4929</v>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东海佳同康持有474000股，持股比例1.4929%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>59</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>国药中生</t>
+        </is>
+      </c>
+      <c r="G258" t="n">
+        <v>46.1846</v>
+      </c>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="n">
+        <v>1.4546</v>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东国药中生持有461846股，持股比例1.4546%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>59</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>苏州敦行</t>
+        </is>
+      </c>
+      <c r="G259" t="n">
+        <v>40</v>
+      </c>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="n">
+        <v>1.2598</v>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东苏州敦行持有400000股，持股比例1.2598%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>59</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>夏尔巴二期</t>
+        </is>
+      </c>
+      <c r="G260" t="n">
+        <v>39.2954</v>
+      </c>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="n">
+        <v>1.2376</v>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东夏尔巴二期持有392954股，持股比例1.2376%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>59</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>陈志华</t>
+        </is>
+      </c>
+      <c r="G261" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="n">
+        <v>0.9461000000000001</v>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东陈志华持有300400股，持股比例0.9461%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>59</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>耿卫东</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>30</v>
+      </c>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="n">
+        <v>0.9449</v>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东耿卫东持有300000股，持股比例0.9449%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>59</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>甘李药业</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>23.5772</v>
+      </c>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="n">
+        <v>0.7426</v>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东甘李药业持有235772股，持股比例0.7426%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>59</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>骏耀投资</t>
+        </is>
+      </c>
+      <c r="G264" t="n">
+        <v>20</v>
+      </c>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="n">
+        <v>0.6299</v>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东骏耀投资持有200000股，持股比例0.6299%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>59</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>朱勤华</t>
+        </is>
+      </c>
+      <c r="G265" t="n">
+        <v>19.4081</v>
+      </c>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="n">
+        <v>0.6113</v>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东朱勤华持有194081股，持股比例0.6113%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>59</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>吴征涛</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>15.7182</v>
+      </c>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="n">
+        <v>0.4951</v>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东吴征涛持有157182股，持股比例0.4951%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>59</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>国药二期</t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>15.5625</v>
+      </c>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="n">
+        <v>0.4901</v>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东国药二期持有155625股，持股比例0.4901%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>59</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>华泰大健康二号</t>
+        </is>
+      </c>
+      <c r="G268" t="n">
+        <v>12.0034</v>
+      </c>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="n">
+        <v>0.3781</v>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东华泰大健康二号持有120034股，持股比例0.3781%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>59</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E269" t="inlineStr"/>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>唐斌</t>
+        </is>
+      </c>
+      <c r="G269" t="n">
+        <v>3.0041</v>
+      </c>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="n">
+        <v>0.0946</v>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东唐斌持有30041股，持股比例0.0946%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>59</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E270" t="inlineStr"/>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>道兴投资</t>
+        </is>
+      </c>
+      <c r="G270" t="n">
+        <v>2.8079</v>
+      </c>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="n">
+        <v>0.08840000000000001</v>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东道兴投资持有28079股，持股比例0.0884%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>59</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>张敏</t>
+        </is>
+      </c>
+      <c r="G271" t="n">
+        <v>2.0654</v>
+      </c>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="n">
+        <v>0.06510000000000001</v>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东张敏持有20654股，持股比例0.0651%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>59</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E272" t="inlineStr"/>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>圣成投资</t>
+        </is>
+      </c>
+      <c r="G272" t="n">
+        <v>0.9699</v>
+      </c>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东圣成投资持有9699股，持股比例0.0305%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>59</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>3175.067</v>
+      </c>
+      <c r="E273" t="inlineStr"/>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>圣祁投资</t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>0.1556</v>
+      </c>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>苏州赛分科技股份有限公司首次公开发行股票，发行前股东圣祁投资持有1556股，持股比例0.0049%（招股书第59页）</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>manual_gold</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>检查项</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>公司代码</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>校验条目</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>PDF披露值</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>计算值</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>差异</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>差异率</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>是否在容差范围内</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>原文证据</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>股权结构存量</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>赛分科技 三表抽取</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>文件包含3个sheet</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>认缴流量</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>subscription=15</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>transfer=2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>持股比例合计</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>各时点持股比例合计</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1000.0207</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>272条快照,比例合计1000.02</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>全部时点</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>认购价格验算</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>国寿疌泉 2021-04-20</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>53.9867</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>金额÷数量=单价</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2021-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>认购价格验算</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>国寿疌泉 2021-04-20</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>53.9867</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>金额÷数量=单价</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2021-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>认购价格验算</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>国寿疌泉 2021-04-20</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>53.9867</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>金额÷数量=单价</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2021-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>认购价格验算</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>国寿疌泉 2021-04-20</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>53.9867</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>金额÷数量=单价</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2021-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>认购价格验算</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>国寿疌泉 2021-04-20</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>53.9867</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>金额÷数量=单价</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2021-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>认购价格验算</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>国寿疌泉 2021-04-20</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>53.9867</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>金额÷数量=单价</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2021-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>认购价格验算</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>国寿疌泉 2021-04-20</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>53.9867</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>金额÷数量=单价</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2021-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>认购价格验算</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>国寿疌泉 2021-04-20</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>53.9867</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>金额÷数量=单价</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2021-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>认购价格验算</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>国寿疌泉 2021-04-20</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>53.9867</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>金额÷数量=单价</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2021-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>认购价格验算</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>国寿疌泉 2021-04-20</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>53.9867</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>金额÷数量=单价</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2021-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>认购价格验算</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>国寿疌泉 2021-04-20</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>53.9867</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>金额÷数量=单价</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2021-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>认购价格验算</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>国寿疌泉 2021-04-20</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>53.9867</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>金额÷数量=单价</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2021-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>认购价格验算</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>国寿疌泉 2021-04-20</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>53.9867</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>金额÷数量=单价</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2021-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>认购价格验算</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>国寿疌泉 2021-04-20</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>53.9867</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>金额÷数量=单价</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2021-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>认购价格验算</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>国寿疌泉 2021-04-20</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>53.9867</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2021年2月25日，赛分有限召开股东会并作出决议，同意公司注册资本增加 342.6769 万元至 2,750.6769 万元。新增的 342.6769 万元注册资本由国寿疌泉、复星惟盈、唐斌、张敏以</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>金额÷数量=单价</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2021-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>持股比例合计</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>4、2021年 11月，报告期内第二次增资 | 增资完成后 (31名股东)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>100.0000%</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.0000%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>合计100.00%</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>4、2021年 11月，报告期内第二次增资 | 增资完成后</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>持股比例合计</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>5、2021年 12月，报告期内第三次增资 | 增资完成后 (32名股东)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>100.0001%</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.0001%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>合计100.00%</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>5、2021年 12月，报告期内第三次增资 | 增资完成后</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>持股比例合计</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后 (32名股东)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>100.0001%</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.0001%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>合计100.00%</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>6、2021年 12月，报告期内第一次资本公积转增股本 | 增资完成后</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>持股比例合计</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表） (31名股东)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>100.0000%</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.0000%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>合计100.00%</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>发行前（第59页股东表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>持股比例合计</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>报告期初 | 设立时 (16名股东)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>100.0200%</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>合计100.02%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>报告期初 | 设立时</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>持股比例合计</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>（2）报告期内第一次增资 | 2、2021年 8月，报告期内第二次股权转让 (21名股东)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>100.0001%</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.0001%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>合计100.00%</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>（2）报告期内第一次增资 | 2、2021年 8月，报告期内第二次股权转让</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>持股比例合计</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>（2）报告期内第一次增资 | 报告期初 (21名股东)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>100.0001%</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.0001%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>合计100.00%</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>（2）报告期内第一次增资 | 报告期初</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>持股比例合计</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>（一）公司前身赛分有限的设立情况 | 设立时 (3名股东)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>100.0000%</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.0000%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>合计100.00%</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>（一）公司前身赛分有限的设立情况 | 设立时</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>持股比例合计</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>（一）公司股权关系 | 增资完成后 (32名股东)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>100.0001%</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0.0001%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>合计100.00%</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>（一）公司股权关系 | 增资完成后</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>持股比例合计</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>688758</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>（二）实际控制人控制的其他企业情况 | 1、苏州贤达 (15名股东)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>100.0002%</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0.0002%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>合计100.00%</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>（二）实际控制人控制的其他企业情况 | 1、苏州贤达</t>
         </is>
       </c>
     </row>
